--- a/PERSONAL_CLAUDE.xlsx
+++ b/PERSONAL_CLAUDE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4263" uniqueCount="1975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4401" uniqueCount="2023">
   <si>
     <t>id_persona</t>
   </si>
@@ -4401,6 +4401,12 @@
     <t>Caballero de la Orden de San Genaro</t>
   </si>
   <si>
+    <t>TP0044</t>
+  </si>
+  <si>
+    <t>31/03/1772</t>
+  </si>
+  <si>
     <t>id_ascenso</t>
   </si>
   <si>
@@ -4983,6 +4989,96 @@
     <t>ASC0000149</t>
   </si>
   <si>
+    <t>ASC0000150</t>
+  </si>
+  <si>
+    <t>GR02</t>
+  </si>
+  <si>
+    <t>06/11/1738</t>
+  </si>
+  <si>
+    <t>ASC0000151</t>
+  </si>
+  <si>
+    <t>04/05/1748</t>
+  </si>
+  <si>
+    <t>ASC0000152</t>
+  </si>
+  <si>
+    <t>04/08/1753</t>
+  </si>
+  <si>
+    <t>ASC0000153</t>
+  </si>
+  <si>
+    <t>11/04/1769</t>
+  </si>
+  <si>
+    <t>ASC0000154</t>
+  </si>
+  <si>
+    <t>24/08/1779</t>
+  </si>
+  <si>
+    <t>ASC0000155</t>
+  </si>
+  <si>
+    <t>29/06/1762</t>
+  </si>
+  <si>
+    <t>ASC0000156</t>
+  </si>
+  <si>
+    <t>GR01</t>
+  </si>
+  <si>
+    <t>09/11/1737</t>
+  </si>
+  <si>
+    <t>ASC0000157</t>
+  </si>
+  <si>
+    <t>19/11/1740</t>
+  </si>
+  <si>
+    <t>ASC0000158</t>
+  </si>
+  <si>
+    <t>GR03</t>
+  </si>
+  <si>
+    <t>13/05/1744</t>
+  </si>
+  <si>
+    <t>ASC0000159</t>
+  </si>
+  <si>
+    <t>ASC0000160</t>
+  </si>
+  <si>
+    <t>20/11/1749</t>
+  </si>
+  <si>
+    <t>ASC0000161</t>
+  </si>
+  <si>
+    <t>20/03/1754</t>
+  </si>
+  <si>
+    <t>ASC0000162</t>
+  </si>
+  <si>
+    <t>13/12/1760</t>
+  </si>
+  <si>
+    <t>ASC0000163</t>
+  </si>
+  <si>
+    <t>29/06/1769</t>
+  </si>
+  <si>
     <t>id_destino_mar</t>
   </si>
   <si>
@@ -5082,9 +5178,6 @@
     <t>DESM000005</t>
   </si>
   <si>
-    <t>GR03</t>
-  </si>
-  <si>
     <t>Alférez de navío</t>
   </si>
   <si>
@@ -5151,9 +5244,6 @@
     <t>DESM000015</t>
   </si>
   <si>
-    <t>GR02</t>
-  </si>
-  <si>
     <t>Alférez de fragata</t>
   </si>
   <si>
@@ -5205,9 +5295,6 @@
     <t>DESM000021</t>
   </si>
   <si>
-    <t>GR01</t>
-  </si>
-  <si>
     <t>Guardia marina</t>
   </si>
   <si>
@@ -5553,6 +5640,51 @@
     <t>DESM000065</t>
   </si>
   <si>
+    <t>DESM000066</t>
+  </si>
+  <si>
+    <t>BUQ00122</t>
+  </si>
+  <si>
+    <t>Lebrel</t>
+  </si>
+  <si>
+    <t>Jabeque</t>
+  </si>
+  <si>
+    <t>DESM000067</t>
+  </si>
+  <si>
+    <t>05/05/1775</t>
+  </si>
+  <si>
+    <t>17/08/1775</t>
+  </si>
+  <si>
+    <t>DESM000068</t>
+  </si>
+  <si>
+    <t>BUQ00111</t>
+  </si>
+  <si>
+    <t>Esmeralda</t>
+  </si>
+  <si>
+    <t>DESM000069</t>
+  </si>
+  <si>
+    <t>18/08/1775</t>
+  </si>
+  <si>
+    <t>DESM000070</t>
+  </si>
+  <si>
+    <t>BUQ00120</t>
+  </si>
+  <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
     <t>id_destino_tierra</t>
   </si>
   <si>
@@ -5772,6 +5904,9 @@
     <t>DEST016</t>
   </si>
   <si>
+    <t>31/06/1776</t>
+  </si>
+  <si>
     <t>DEST017</t>
   </si>
   <si>
@@ -5920,6 +6055,15 @@
   </si>
   <si>
     <t>BUQ00106</t>
+  </si>
+  <si>
+    <t>MANE00009</t>
+  </si>
+  <si>
+    <t>ESC0008</t>
+  </si>
+  <si>
+    <t>Escuadra de patrulla García del Postigo</t>
   </si>
   <si>
     <t>id_plana_escuadra</t>
@@ -6026,7 +6170,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -6089,11 +6233,17 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -15196,6 +15346,29 @@
         <v>1459</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="6" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>1461</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -15214,7 +15387,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -15223,19 +15396,19 @@
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="G1" s="5"/>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>20</v>
@@ -15244,18 +15417,18 @@
         <v>21</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>20</v>
@@ -15264,18 +15437,18 @@
         <v>21</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>44</v>
@@ -15284,18 +15457,18 @@
         <v>45</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>167</v>
@@ -15304,18 +15477,18 @@
         <v>168</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>1477</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>171</v>
@@ -15324,18 +15497,18 @@
         <v>172</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>1477</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>177</v>
@@ -15344,18 +15517,18 @@
         <v>178</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>1477</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>184</v>
@@ -15364,18 +15537,18 @@
         <v>185</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>1477</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>190</v>
@@ -15384,18 +15557,18 @@
         <v>191</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>1477</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>194</v>
@@ -15404,18 +15577,18 @@
         <v>195</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>1477</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>214</v>
@@ -15424,18 +15597,18 @@
         <v>215</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>218</v>
@@ -15444,18 +15617,18 @@
         <v>219</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>220</v>
@@ -15464,18 +15637,18 @@
         <v>221</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>223</v>
@@ -15484,18 +15657,18 @@
         <v>224</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>226</v>
@@ -15504,18 +15677,18 @@
         <v>227</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>228</v>
@@ -15524,18 +15697,18 @@
         <v>229</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>240</v>
@@ -15544,18 +15717,18 @@
         <v>241</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>242</v>
@@ -15564,18 +15737,18 @@
         <v>243</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>244</v>
@@ -15584,18 +15757,18 @@
         <v>245</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>246</v>
@@ -15604,18 +15777,18 @@
         <v>247</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>248</v>
@@ -15624,18 +15797,18 @@
         <v>249</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>250</v>
@@ -15644,18 +15817,18 @@
         <v>251</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>252</v>
@@ -15664,18 +15837,18 @@
         <v>253</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>254</v>
@@ -15684,18 +15857,18 @@
         <v>255</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>256</v>
@@ -15704,18 +15877,18 @@
         <v>257</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>258</v>
@@ -15724,18 +15897,18 @@
         <v>259</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>260</v>
@@ -15744,18 +15917,18 @@
         <v>261</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>265</v>
@@ -15764,18 +15937,18 @@
         <v>266</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>267</v>
@@ -15784,18 +15957,18 @@
         <v>268</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>271</v>
@@ -15804,18 +15977,18 @@
         <v>272</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>171</v>
@@ -15824,18 +15997,18 @@
         <v>172</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>199</v>
@@ -15844,18 +16017,18 @@
         <v>200</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>411</v>
@@ -15864,18 +16037,18 @@
         <v>412</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>445</v>
@@ -15884,18 +16057,18 @@
         <v>446</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>413</v>
@@ -15904,38 +16077,38 @@
         <v>414</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>425</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>427</v>
@@ -15944,18 +16117,18 @@
         <v>428</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>429</v>
@@ -15964,18 +16137,18 @@
         <v>430</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>431</v>
@@ -15984,18 +16157,18 @@
         <v>432</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>433</v>
@@ -16004,18 +16177,18 @@
         <v>434</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>435</v>
@@ -16024,18 +16197,18 @@
         <v>436</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>437</v>
@@ -16044,18 +16217,18 @@
         <v>438</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>439</v>
@@ -16064,18 +16237,18 @@
         <v>440</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>315</v>
@@ -16084,18 +16257,18 @@
         <v>316</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>317</v>
@@ -16104,18 +16277,18 @@
         <v>318</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>353</v>
@@ -16124,18 +16297,18 @@
         <v>354</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>267</v>
@@ -16144,18 +16317,18 @@
         <v>268</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>27</v>
@@ -16164,18 +16337,18 @@
         <v>28</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>44</v>
@@ -16184,18 +16357,18 @@
         <v>45</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>531</v>
@@ -16204,18 +16377,18 @@
         <v>532</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>533</v>
@@ -16224,18 +16397,18 @@
         <v>534</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>535</v>
@@ -16244,18 +16417,18 @@
         <v>536</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>537</v>
@@ -16264,18 +16437,18 @@
         <v>538</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>539</v>
@@ -16284,18 +16457,18 @@
         <v>540</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>541</v>
@@ -16304,18 +16477,18 @@
         <v>542</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>543</v>
@@ -16324,18 +16497,18 @@
         <v>544</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>545</v>
@@ -16344,18 +16517,18 @@
         <v>546</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>547</v>
@@ -16364,18 +16537,18 @@
         <v>548</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>549</v>
@@ -16384,18 +16557,18 @@
         <v>550</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>551</v>
@@ -16404,18 +16577,18 @@
         <v>552</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>553</v>
@@ -16424,18 +16597,18 @@
         <v>554</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>555</v>
@@ -16444,18 +16617,18 @@
         <v>556</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>557</v>
@@ -16464,18 +16637,18 @@
         <v>558</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>559</v>
@@ -16484,18 +16657,18 @@
         <v>560</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>561</v>
@@ -16504,18 +16677,18 @@
         <v>562</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>563</v>
@@ -16524,18 +16697,18 @@
         <v>564</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>565</v>
@@ -16544,38 +16717,38 @@
         <v>566</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>567</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>569</v>
@@ -16584,18 +16757,18 @@
         <v>570</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>571</v>
@@ -16604,18 +16777,18 @@
         <v>572</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>573</v>
@@ -16624,18 +16797,18 @@
         <v>574</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>575</v>
@@ -16644,18 +16817,18 @@
         <v>576</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>577</v>
@@ -16664,18 +16837,18 @@
         <v>578</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>579</v>
@@ -16684,18 +16857,18 @@
         <v>580</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>27</v>
@@ -16704,18 +16877,18 @@
         <v>28</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>267</v>
@@ -16724,15 +16897,15 @@
         <v>268</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>267</v>
@@ -16741,18 +16914,18 @@
         <v>268</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>271</v>
@@ -16761,18 +16934,18 @@
         <v>272</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>202</v>
@@ -16781,18 +16954,18 @@
         <v>203</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>230</v>
@@ -16801,18 +16974,18 @@
         <v>231</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>214</v>
@@ -16821,18 +16994,18 @@
         <v>215</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>583</v>
@@ -16841,18 +17014,18 @@
         <v>584</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>232</v>
@@ -16861,18 +17034,18 @@
         <v>233</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>234</v>
@@ -16881,18 +17054,18 @@
         <v>235</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>585</v>
@@ -16901,18 +17074,18 @@
         <v>586</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>218</v>
@@ -16921,18 +17094,18 @@
         <v>219</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>220</v>
@@ -16941,18 +17114,18 @@
         <v>221</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>223</v>
@@ -16961,18 +17134,18 @@
         <v>224</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>587</v>
@@ -16981,18 +17154,18 @@
         <v>588</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>226</v>
@@ -17001,18 +17174,18 @@
         <v>227</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>228</v>
@@ -17021,18 +17194,18 @@
         <v>229</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>171</v>
@@ -17041,18 +17214,18 @@
         <v>172</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>242</v>
@@ -17061,18 +17234,18 @@
         <v>243</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>246</v>
@@ -17081,18 +17254,18 @@
         <v>247</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>256</v>
@@ -17101,18 +17274,18 @@
         <v>257</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>260</v>
@@ -17121,18 +17294,18 @@
         <v>261</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>389</v>
@@ -17141,18 +17314,18 @@
         <v>390</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>439</v>
@@ -17161,18 +17334,18 @@
         <v>440</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>479</v>
@@ -17181,18 +17354,18 @@
         <v>480</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>481</v>
@@ -17201,18 +17374,18 @@
         <v>482</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>451</v>
@@ -17221,18 +17394,18 @@
         <v>452</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>605</v>
@@ -17241,12 +17414,12 @@
         <v>606</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>620</v>
@@ -17255,12 +17428,12 @@
         <v>621</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>657</v>
@@ -17269,12 +17442,12 @@
         <v>658</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>517</v>
@@ -17283,18 +17456,18 @@
         <v>518</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>461</v>
@@ -17303,18 +17476,18 @@
         <v>462</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>465</v>
@@ -17323,18 +17496,18 @@
         <v>466</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>467</v>
@@ -17343,18 +17516,18 @@
         <v>468</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>477</v>
@@ -17363,18 +17536,18 @@
         <v>478</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>493</v>
@@ -17383,18 +17556,18 @@
         <v>494</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>283</v>
@@ -17403,18 +17576,18 @@
         <v>284</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>397</v>
@@ -17423,18 +17596,18 @@
         <v>398</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>369</v>
@@ -17443,18 +17616,18 @@
         <v>370</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>365</v>
@@ -17463,18 +17636,18 @@
         <v>366</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E114" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>503</v>
@@ -17483,18 +17656,18 @@
         <v>504</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>491</v>
@@ -17503,18 +17676,18 @@
         <v>492</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>888</v>
@@ -17523,18 +17696,18 @@
         <v>889</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>622</v>
@@ -17543,18 +17716,18 @@
         <v>623</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>614</v>
@@ -17563,18 +17736,18 @@
         <v>615</v>
       </c>
       <c r="D119" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E119" s="11" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F119" s="6" t="s">
         <v>1477</v>
-      </c>
-      <c r="E119" s="11" t="s">
-        <v>1507</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>624</v>
@@ -17583,18 +17756,18 @@
         <v>625</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>220</v>
@@ -17603,18 +17776,18 @@
         <v>221</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>303</v>
@@ -17623,18 +17796,18 @@
         <v>304</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E122" s="11" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>283</v>
@@ -17643,18 +17816,18 @@
         <v>284</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>671</v>
@@ -17663,18 +17836,18 @@
         <v>672</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>673</v>
@@ -17683,18 +17856,18 @@
         <v>674</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>675</v>
@@ -17703,18 +17876,18 @@
         <v>676</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>667</v>
@@ -17723,18 +17896,18 @@
         <v>668</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E127" s="11" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>507</v>
@@ -17743,18 +17916,18 @@
         <v>508</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>163</v>
@@ -17763,18 +17936,18 @@
         <v>164</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E129" s="11" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="6" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>932</v>
@@ -17783,18 +17956,18 @@
         <v>933</v>
       </c>
       <c r="D130" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E130" s="11" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F130" s="6" t="s">
         <v>1477</v>
-      </c>
-      <c r="E130" s="11" t="s">
-        <v>1507</v>
-      </c>
-      <c r="F130" s="6" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>932</v>
@@ -17803,18 +17976,18 @@
         <v>933</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>934</v>
@@ -17823,18 +17996,18 @@
         <v>935</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>1011</v>
@@ -17843,18 +18016,18 @@
         <v>1012</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>541</v>
@@ -17863,18 +18036,18 @@
         <v>542</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>1198</v>
@@ -17883,18 +18056,18 @@
         <v>1199</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>1200</v>
@@ -17903,18 +18076,18 @@
         <v>1201</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>1202</v>
@@ -17923,18 +18096,18 @@
         <v>1203</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E137" s="11" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>1204</v>
@@ -17943,18 +18116,18 @@
         <v>1205</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E138" s="11" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>1206</v>
@@ -17963,18 +18136,18 @@
         <v>1207</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E139" s="11" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>1208</v>
@@ -17983,18 +18156,18 @@
         <v>1209</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E140" s="11" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>1009</v>
@@ -18003,18 +18176,18 @@
         <v>1010</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>840</v>
@@ -18023,18 +18196,18 @@
         <v>841</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>818</v>
@@ -18043,18 +18216,18 @@
         <v>819</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>846</v>
@@ -18063,18 +18236,18 @@
         <v>847</v>
       </c>
       <c r="D144" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>878</v>
@@ -18083,18 +18256,18 @@
         <v>879</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>940</v>
@@ -18103,18 +18276,18 @@
         <v>941</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>942</v>
@@ -18123,18 +18296,18 @@
         <v>943</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>533</v>
@@ -18143,18 +18316,18 @@
         <v>534</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>549</v>
@@ -18163,18 +18336,18 @@
         <v>550</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>561</v>
@@ -18183,13 +18356,251 @@
         <v>562</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>1600</v>
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E151" s="11" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E152" s="11" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E153" s="11" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E154" s="11" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C155" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>1467</v>
+      </c>
+      <c r="E155" s="11" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C156" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E156" s="11" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C157" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>1670</v>
+      </c>
+      <c r="E157" s="11" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C158" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C159" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E159" s="11" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C160" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E160" s="11" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C161" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C162" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E162" s="11" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C163" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E163" s="8" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C164" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>1467</v>
+      </c>
+      <c r="E164" s="11" t="s">
+        <v>1685</v>
       </c>
     </row>
   </sheetData>
@@ -18211,7 +18622,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1654</v>
+        <v>1686</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>0</v>
@@ -18220,42 +18631,42 @@
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>1655</v>
+        <v>1687</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>1656</v>
+        <v>1688</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>1657</v>
+        <v>1689</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>1658</v>
+        <v>1690</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>1659</v>
+        <v>1691</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>1660</v>
+        <v>1692</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>1661</v>
+        <v>1693</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1662</v>
+        <v>1694</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>1663</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>1664</v>
+        <v>1696</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>16</v>
@@ -18264,38 +18675,38 @@
         <v>17</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1666</v>
+        <v>1698</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>1667</v>
+        <v>1699</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
       <c r="M2" s="19" t="s">
-        <v>1671</v>
+        <v>1703</v>
       </c>
       <c r="N2" s="19" t="s">
-        <v>1671</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>1672</v>
+        <v>1704</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>25</v>
@@ -18304,33 +18715,33 @@
         <v>26</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1673</v>
+        <v>1705</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1674</v>
+        <v>1706</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>1677</v>
+        <v>1709</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>27</v>
@@ -18339,33 +18750,33 @@
         <v>28</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>1673</v>
+        <v>1705</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1674</v>
+        <v>1706</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1678</v>
+        <v>1710</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>1679</v>
+        <v>1711</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>1680</v>
+        <v>1712</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>18</v>
@@ -18374,36 +18785,36 @@
         <v>19</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>1681</v>
+        <v>1713</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1682</v>
+        <v>1714</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>1683</v>
+        <v>1715</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>1685</v>
+        <v>1717</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>1685</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>1686</v>
+        <v>1718</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>34</v>
@@ -18412,33 +18823,33 @@
         <v>35</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1687</v>
+        <v>1675</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>1688</v>
+        <v>1719</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>1674</v>
+        <v>1706</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1689</v>
+        <v>1720</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1690</v>
+        <v>1721</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>1691</v>
+        <v>1722</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>44</v>
@@ -18447,30 +18858,30 @@
         <v>45</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>1693</v>
+        <v>1724</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>1694</v>
+        <v>1725</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>1695</v>
+        <v>1726</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>46</v>
@@ -18479,30 +18890,30 @@
         <v>47</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>1693</v>
+        <v>1724</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>1694</v>
+        <v>1725</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1678</v>
+        <v>1710</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>1679</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>1696</v>
+        <v>1727</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>61</v>
@@ -18511,33 +18922,33 @@
         <v>62</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>1681</v>
+        <v>1713</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>1682</v>
+        <v>1714</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>1683</v>
+        <v>1715</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>1697</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>1698</v>
+        <v>1729</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>36</v>
@@ -18546,33 +18957,33 @@
         <v>37</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>1682</v>
+        <v>1714</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>1683</v>
+        <v>1715</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1678</v>
+        <v>1710</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>1679</v>
+        <v>1711</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>1697</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>1699</v>
+        <v>1730</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>36</v>
@@ -18581,39 +18992,39 @@
         <v>37</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>1681</v>
+        <v>1713</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>1682</v>
+        <v>1714</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>1683</v>
+        <v>1715</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>1700</v>
+        <v>1731</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>1685</v>
+        <v>1717</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>1685</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>1701</v>
+        <v>1732</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>63</v>
@@ -18622,33 +19033,33 @@
         <v>64</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F12" s="6" t="s">
+        <v>1733</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>1734</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>1716</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>1701</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>1702</v>
       </c>
-      <c r="G12" s="12" t="s">
-        <v>1703</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>1684</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>1669</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>1670</v>
-      </c>
       <c r="K12" s="11" t="s">
-        <v>1704</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>1705</v>
+        <v>1736</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>130</v>
@@ -18657,33 +19068,33 @@
         <v>131</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="E13" s="7" t="s">
+        <v>1737</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>1706</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>1674</v>
-      </c>
       <c r="G13" s="12" t="s">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>1689</v>
+        <v>1720</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1690</v>
+        <v>1721</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>1707</v>
+        <v>1738</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>132</v>
@@ -18692,33 +19103,33 @@
         <v>133</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="E14" s="7" t="s">
+        <v>1737</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>1706</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>1674</v>
-      </c>
       <c r="G14" s="12" t="s">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>1689</v>
+        <v>1720</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1690</v>
+        <v>1721</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>1708</v>
+        <v>1739</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>134</v>
@@ -18727,33 +19138,33 @@
         <v>135</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1687</v>
+        <v>1675</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>1688</v>
+        <v>1719</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>1674</v>
+        <v>1706</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>1689</v>
+        <v>1720</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1690</v>
+        <v>1721</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>1709</v>
+        <v>1740</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>136</v>
@@ -18762,33 +19173,33 @@
         <v>137</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1710</v>
+        <v>1657</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1711</v>
+        <v>1741</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1674</v>
+        <v>1706</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>1689</v>
+        <v>1720</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>1690</v>
+        <v>1721</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>1712</v>
+        <v>1742</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>138</v>
@@ -18797,27 +19208,27 @@
         <v>139</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>1674</v>
+        <v>1706</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>1713</v>
+        <v>1743</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>1714</v>
+        <v>1744</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>1715</v>
+        <v>1745</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>140</v>
@@ -18826,27 +19237,27 @@
         <v>141</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>1674</v>
+        <v>1706</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>1716</v>
+        <v>1746</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>1717</v>
+        <v>1747</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>1718</v>
+        <v>1748</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>142</v>
@@ -18855,27 +19266,27 @@
         <v>143</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>1674</v>
+        <v>1706</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>1719</v>
+        <v>1749</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>1720</v>
+        <v>1750</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>1721</v>
+        <v>1751</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>144</v>
@@ -18884,27 +19295,27 @@
         <v>145</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>1674</v>
+        <v>1706</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>1722</v>
+        <v>1752</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>1723</v>
+        <v>1753</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>1724</v>
+        <v>1754</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>146</v>
@@ -18913,27 +19324,27 @@
         <v>147</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>1674</v>
+        <v>1706</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>1725</v>
+        <v>1755</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>1726</v>
+        <v>1756</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
-        <v>1727</v>
+        <v>1757</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>148</v>
@@ -18942,33 +19353,33 @@
         <v>149</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1728</v>
+        <v>1670</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>1729</v>
+        <v>1758</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>1674</v>
+        <v>1706</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>1730</v>
+        <v>1759</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>1729</v>
+        <v>1758</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
-        <v>1731</v>
+        <v>1760</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>150</v>
@@ -18977,33 +19388,33 @@
         <v>151</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1728</v>
+        <v>1670</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>1729</v>
+        <v>1758</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>1674</v>
+        <v>1706</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>1675</v>
+        <v>1707</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>1730</v>
+        <v>1759</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>1729</v>
+        <v>1758</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>1732</v>
+        <v>1761</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>267</v>
@@ -19012,36 +19423,36 @@
         <v>268</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>1681</v>
+        <v>1713</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>1733</v>
+        <v>1762</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>1734</v>
+        <v>1763</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>1735</v>
+        <v>1764</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>1736</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>1737</v>
+        <v>1766</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>299</v>
@@ -19050,30 +19461,30 @@
         <v>300</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>1738</v>
+        <v>1767</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>1739</v>
+        <v>1768</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>1740</v>
+        <v>1769</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>252</v>
@@ -19082,30 +19493,30 @@
         <v>253</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>1681</v>
+        <v>1713</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>1741</v>
+        <v>1770</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>1742</v>
+        <v>1771</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="s">
-        <v>1743</v>
+        <v>1772</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>461</v>
@@ -19114,33 +19525,33 @@
         <v>462</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>1673</v>
+        <v>1705</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>1744</v>
+        <v>1773</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>1745</v>
+        <v>1774</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>1689</v>
+        <v>1720</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>1690</v>
+        <v>1721</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>1746</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="s">
-        <v>1747</v>
+        <v>1776</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>256</v>
@@ -19149,30 +19560,30 @@
         <v>257</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1681</v>
+        <v>1713</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>1748</v>
+        <v>1777</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>1749</v>
+        <v>1778</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>1750</v>
+        <v>1779</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>431</v>
@@ -19181,30 +19592,30 @@
         <v>432</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>1751</v>
+        <v>1780</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>1752</v>
+        <v>1781</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>1753</v>
+        <v>1782</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>413</v>
@@ -19213,30 +19624,30 @@
         <v>414</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>1744</v>
+        <v>1773</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>1745</v>
+        <v>1774</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
-        <v>1754</v>
+        <v>1783</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>519</v>
@@ -19245,24 +19656,24 @@
         <v>520</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>1682</v>
+        <v>1714</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>1683</v>
+        <v>1715</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>1755</v>
+        <v>1784</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>1756</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>1757</v>
+        <v>1786</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>521</v>
@@ -19271,50 +19682,50 @@
         <v>522</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>1682</v>
+        <v>1714</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>1683</v>
+        <v>1715</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>1758</v>
+        <v>1787</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>1759</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>1760</v>
+        <v>1789</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>523</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>1761</v>
+        <v>1790</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>1682</v>
+        <v>1714</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>1683</v>
+        <v>1715</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>1755</v>
+        <v>1784</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>1756</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>1762</v>
+        <v>1791</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>267</v>
@@ -19323,30 +19734,30 @@
         <v>268</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>1763</v>
+        <v>1792</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>1764</v>
+        <v>1793</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>1765</v>
+        <v>1794</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>531</v>
@@ -19355,24 +19766,24 @@
         <v>532</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>1673</v>
+        <v>1705</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>1763</v>
+        <v>1792</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>1764</v>
+        <v>1793</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="s">
-        <v>1766</v>
+        <v>1795</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>429</v>
@@ -19381,30 +19792,30 @@
         <v>430</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>1767</v>
+        <v>1796</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>1768</v>
+        <v>1797</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="s">
-        <v>1769</v>
+        <v>1798</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>18</v>
@@ -19413,25 +19824,25 @@
         <v>19</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>1770</v>
+        <v>1799</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>1771</v>
+        <v>1800</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="L37" s="8"/>
       <c r="N37" s="11" t="s">
@@ -19440,7 +19851,7 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="s">
-        <v>1772</v>
+        <v>1801</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>340</v>
@@ -19449,25 +19860,25 @@
         <v>341</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>1773</v>
+        <v>1802</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>1774</v>
+        <v>1803</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="L38" s="11"/>
       <c r="N38" s="11" t="s">
@@ -19476,7 +19887,7 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="s">
-        <v>1775</v>
+        <v>1804</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>271</v>
@@ -19485,30 +19896,30 @@
         <v>272</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>1681</v>
+        <v>1713</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>1776</v>
+        <v>1805</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>1777</v>
+        <v>1806</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="s">
-        <v>1778</v>
+        <v>1807</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>479</v>
@@ -19517,30 +19928,30 @@
         <v>480</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>1779</v>
+        <v>1808</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>1780</v>
+        <v>1809</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="s">
-        <v>1781</v>
+        <v>1810</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>481</v>
@@ -19549,30 +19960,30 @@
         <v>482</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>1782</v>
+        <v>1811</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>1783</v>
+        <v>1812</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
-        <v>1784</v>
+        <v>1813</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>325</v>
@@ -19581,33 +19992,33 @@
         <v>326</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>1681</v>
+        <v>1713</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>1785</v>
+        <v>1814</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>1786</v>
+        <v>1815</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="L42" s="11" t="s">
-        <v>1787</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>1788</v>
+        <v>1817</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>559</v>
@@ -19616,33 +20027,33 @@
         <v>560</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>1789</v>
+        <v>1818</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>1790</v>
+        <v>1819</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="L43" s="11" t="s">
-        <v>1791</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>1792</v>
+        <v>1821</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>455</v>
@@ -19651,30 +20062,30 @@
         <v>456</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>1793</v>
+        <v>1822</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>1794</v>
+        <v>1823</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
-        <v>1795</v>
+        <v>1824</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>479</v>
@@ -19683,33 +20094,33 @@
         <v>480</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>1681</v>
+        <v>1713</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>1779</v>
+        <v>1808</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>1780</v>
+        <v>1809</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>1796</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>1797</v>
+        <v>1826</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>764</v>
@@ -19718,33 +20129,33 @@
         <v>765</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>1733</v>
+        <v>1762</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>1734</v>
+        <v>1763</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>1678</v>
+        <v>1710</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>1679</v>
+        <v>1711</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>1735</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>1798</v>
+        <v>1827</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>840</v>
@@ -19753,33 +20164,33 @@
         <v>841</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>1733</v>
+        <v>1762</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>1734</v>
+        <v>1763</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>1689</v>
+        <v>1720</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>1690</v>
+        <v>1721</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>1735</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>1799</v>
+        <v>1828</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>463</v>
@@ -19788,33 +20199,33 @@
         <v>464</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>1800</v>
+        <v>1829</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>1801</v>
+        <v>1830</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>1735</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>1802</v>
+        <v>1831</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>429</v>
@@ -19823,33 +20234,33 @@
         <v>430</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>1803</v>
+        <v>1832</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>1804</v>
+        <v>1833</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>1735</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>1805</v>
+        <v>1834</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>485</v>
@@ -19858,33 +20269,33 @@
         <v>486</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>1806</v>
+        <v>1835</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>1807</v>
+        <v>1836</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>1668</v>
+        <v>1700</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>1735</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>1808</v>
+        <v>1837</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>401</v>
@@ -19893,30 +20304,30 @@
         <v>402</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>1809</v>
+        <v>1838</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>1810</v>
+        <v>1839</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>1811</v>
+        <v>1840</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>894</v>
@@ -19925,30 +20336,30 @@
         <v>895</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>1809</v>
+        <v>1838</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>1810</v>
+        <v>1839</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>1678</v>
+        <v>1710</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>1679</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>1812</v>
+        <v>1841</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>333</v>
@@ -19957,25 +20368,25 @@
         <v>334</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>1681</v>
+        <v>1713</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>1813</v>
+        <v>1842</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>1814</v>
+        <v>1843</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="N53" s="11" t="s">
         <v>335</v>
@@ -19983,7 +20394,7 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="s">
-        <v>1815</v>
+        <v>1844</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>451</v>
@@ -19992,25 +20403,25 @@
         <v>452</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>1813</v>
+        <v>1842</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>1814</v>
+        <v>1843</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>1678</v>
+        <v>1710</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>1679</v>
+        <v>1711</v>
       </c>
       <c r="L54" s="11"/>
       <c r="N54" s="11" t="s">
@@ -20019,7 +20430,7 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="s">
-        <v>1816</v>
+        <v>1845</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>451</v>
@@ -20028,25 +20439,25 @@
         <v>452</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>1681</v>
+        <v>1713</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>1813</v>
+        <v>1842</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>1814</v>
+        <v>1843</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="L55" s="11" t="s">
         <v>335</v>
@@ -20057,7 +20468,7 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="s">
-        <v>1817</v>
+        <v>1846</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>739</v>
@@ -20066,25 +20477,25 @@
         <v>740</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>1813</v>
+        <v>1842</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>1814</v>
+        <v>1843</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>1678</v>
+        <v>1710</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>1679</v>
+        <v>1711</v>
       </c>
       <c r="L56" s="11" t="s">
         <v>335</v>
@@ -20095,7 +20506,7 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="s">
-        <v>1818</v>
+        <v>1847</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>925</v>
@@ -20104,24 +20515,24 @@
         <v>926</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>1748</v>
+        <v>1777</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>1749</v>
+        <v>1778</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>1722</v>
+        <v>1752</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>1723</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
-        <v>1819</v>
+        <v>1848</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>351</v>
@@ -20130,30 +20541,30 @@
         <v>352</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>1741</v>
+        <v>1770</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>1742</v>
+        <v>1771</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="s">
-        <v>1820</v>
+        <v>1849</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>244</v>
@@ -20162,24 +20573,24 @@
         <v>245</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>1821</v>
+        <v>1850</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>1822</v>
+        <v>1851</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="s">
-        <v>1823</v>
+        <v>1852</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>794</v>
@@ -20188,25 +20599,25 @@
         <v>795</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>1824</v>
+        <v>1853</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>1825</v>
+        <v>1854</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="L60" s="6">
         <v>1786.0</v>
@@ -20217,7 +20628,7 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>1826</v>
+        <v>1855</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>1287</v>
@@ -20226,27 +20637,27 @@
         <v>1288</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>1827</v>
+        <v>1856</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>1828</v>
+        <v>1857</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>1670</v>
-      </c>
-      <c r="L61" s="11" t="s">
-        <v>1829</v>
+        <v>1702</v>
+      </c>
+      <c r="N61" s="11" t="s">
+        <v>1858</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="s">
-        <v>1830</v>
+        <v>1859</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>1290</v>
@@ -20255,24 +20666,24 @@
         <v>1291</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>1831</v>
+        <v>1860</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>1832</v>
+        <v>1861</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>1833</v>
+        <v>1862</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
-        <v>1834</v>
+        <v>1863</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>177</v>
@@ -20281,36 +20692,36 @@
         <v>178</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>1835</v>
+        <v>1864</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>1836</v>
+        <v>1865</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="K63" s="6">
         <v>1757.0</v>
       </c>
-      <c r="L63" s="6">
+      <c r="M63" s="6">
         <v>1758.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="s">
-        <v>1837</v>
+        <v>1866</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>1292</v>
@@ -20319,36 +20730,36 @@
         <v>1293</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>1838</v>
+        <v>1867</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>1839</v>
+        <v>1868</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="K64" s="6">
         <v>1757.0</v>
       </c>
-      <c r="L64" s="6">
+      <c r="M64" s="6">
         <v>1758.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="s">
-        <v>1840</v>
+        <v>1869</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>1295</v>
@@ -20357,36 +20768,36 @@
         <v>1296</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>1841</v>
+        <v>1870</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>1842</v>
+        <v>1871</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>1669</v>
+        <v>1701</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>1670</v>
+        <v>1702</v>
       </c>
       <c r="K65" s="6">
         <v>1757.0</v>
       </c>
-      <c r="L65" s="6">
+      <c r="M65" s="6">
         <v>1758.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="s">
-        <v>1843</v>
+        <v>1872</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>240</v>
@@ -20395,25 +20806,209 @@
         <v>241</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>1838</v>
+        <v>1867</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>1839</v>
+        <v>1868</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>1684</v>
+        <v>1716</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>1678</v>
+        <v>1710</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>1679</v>
+        <v>1711</v>
       </c>
       <c r="K66" s="6">
         <v>1757.0</v>
       </c>
-      <c r="L66" s="6">
+      <c r="M66" s="6">
         <v>1758.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>1713</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>1874</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>1875</v>
+      </c>
+      <c r="H67" s="13" t="s">
+        <v>1876</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>1701</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>1702</v>
+      </c>
+      <c r="K67" s="6">
+        <v>1774.0</v>
+      </c>
+      <c r="M67" s="6">
+        <v>1777.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F68" s="12" t="s">
+        <v>1829</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="H68" s="22" t="s">
+        <v>1862</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>1701</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>1702</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>1878</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>1881</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>1882</v>
+      </c>
+      <c r="H69" s="12" t="s">
+        <v>1862</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>1701</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>1702</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>1878</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>1829</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="H70" s="12" t="s">
+        <v>1862</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>1701</v>
+      </c>
+      <c r="J70" s="7" t="s">
+        <v>1702</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>1884</v>
+      </c>
+      <c r="M70" s="6">
+        <v>1778.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>1886</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>1887</v>
+      </c>
+      <c r="H71" s="12" t="s">
+        <v>1876</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>1701</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>1702</v>
+      </c>
+      <c r="K71" s="6">
+        <v>1774.0</v>
+      </c>
+      <c r="M71" s="6">
+        <v>1777.0</v>
       </c>
     </row>
   </sheetData>
@@ -20438,7 +21033,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1844</v>
+        <v>1888</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>0</v>
@@ -20447,39 +21042,39 @@
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>1655</v>
+        <v>1687</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>1845</v>
+        <v>1889</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>1659</v>
+        <v>1691</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>1660</v>
+        <v>1692</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>1661</v>
+        <v>1693</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1662</v>
+        <v>1694</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>1663</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>1846</v>
+        <v>1890</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>13</v>
@@ -20488,33 +21083,33 @@
         <v>14</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>1673</v>
+        <v>1705</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1847</v>
+        <v>1891</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>1848</v>
+        <v>1892</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1849</v>
+        <v>1893</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>1850</v>
-      </c>
-      <c r="L2" s="22" t="s">
-        <v>1851</v>
+        <v>1894</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>1895</v>
       </c>
       <c r="M2" s="19" t="s">
-        <v>1671</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>1852</v>
+        <v>1896</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>16</v>
@@ -20523,33 +21118,33 @@
         <v>17</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1847</v>
+        <v>1891</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>1848</v>
+        <v>1892</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>1849</v>
+        <v>1893</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>1850</v>
+        <v>1894</v>
       </c>
       <c r="J3" s="19" t="s">
-        <v>1671</v>
+        <v>1703</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>1671</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>1853</v>
+        <v>1897</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>20</v>
@@ -20558,71 +21153,71 @@
         <v>21</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>1854</v>
+        <v>1898</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>1855</v>
+        <v>1899</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>1856</v>
-      </c>
-      <c r="I4" s="23" t="s">
-        <v>1857</v>
+        <v>1900</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>1901</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>1858</v>
+        <v>1902</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>1859</v>
+        <v>1903</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>1860</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>1861</v>
+        <v>1905</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1862</v>
+        <v>1906</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>1681</v>
+        <v>1713</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>1854</v>
+        <v>1898</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>1855</v>
+        <v>1899</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>1856</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>1857</v>
+        <v>1900</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>1901</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>1863</v>
+        <v>1907</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>1864</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>1865</v>
+        <v>1909</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>42</v>
@@ -20631,33 +21226,33 @@
         <v>43</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>1692</v>
+        <v>1723</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>1854</v>
+        <v>1898</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>1855</v>
+        <v>1899</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>1856</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>1857</v>
+        <v>1900</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>1901</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>1866</v>
+        <v>1910</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>1867</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>1868</v>
+        <v>1912</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>517</v>
@@ -20666,27 +21261,27 @@
         <v>518</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>1869</v>
+        <v>1913</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>1870</v>
+        <v>1914</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>1871</v>
+        <v>1915</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>1872</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>1873</v>
+        <v>1917</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>184</v>
@@ -20695,27 +21290,27 @@
         <v>185</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>1874</v>
+        <v>1918</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1875</v>
+        <v>1919</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>1876</v>
+        <v>1920</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1877</v>
+        <v>1921</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>1878</v>
+        <v>1922</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>1879</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>1880</v>
+        <v>1924</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>184</v>
@@ -20724,36 +21319,36 @@
         <v>185</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>1881</v>
+        <v>1925</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>1882</v>
+        <v>1926</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1883</v>
+        <v>1927</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>1876</v>
+        <v>1920</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1877</v>
+        <v>1921</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>1879</v>
+        <v>1923</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>1884</v>
+        <v>1928</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>1885</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>1886</v>
+        <v>1930</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>205</v>
@@ -20762,30 +21357,30 @@
         <v>206</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>1887</v>
+        <v>1931</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>1869</v>
+        <v>1913</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1870</v>
+        <v>1914</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>1888</v>
+        <v>1932</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>1889</v>
+        <v>1933</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>1890</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>1891</v>
+        <v>1935</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>624</v>
@@ -20794,22 +21389,22 @@
         <v>625</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>1887</v>
+        <v>1931</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>1869</v>
+        <v>1913</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1870</v>
+        <v>1914</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>1888</v>
+        <v>1932</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>1889</v>
+        <v>1933</v>
       </c>
       <c r="M11" s="11" t="s">
         <v>626</v>
@@ -20817,7 +21412,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>1892</v>
+        <v>1936</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>657</v>
@@ -20826,30 +21421,30 @@
         <v>658</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>1881</v>
+        <v>1925</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>1893</v>
+        <v>1937</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>1894</v>
+        <v>1938</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>1895</v>
+        <v>1939</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>1896</v>
+        <v>1940</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>1897</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>1898</v>
+        <v>1942</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>665</v>
@@ -20858,24 +21453,24 @@
         <v>666</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>1899</v>
+        <v>1943</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>1900</v>
+        <v>1944</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>1901</v>
+        <v>1945</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>1902</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>1903</v>
+        <v>1947</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>159</v>
@@ -20884,22 +21479,22 @@
         <v>160</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>1881</v>
+        <v>1925</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>1904</v>
+        <v>1948</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>1905</v>
+        <v>1949</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>1906</v>
+        <v>1950</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>1907</v>
+        <v>1951</v>
       </c>
       <c r="M14" s="11" t="s">
         <v>162</v>
@@ -20907,7 +21502,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>1908</v>
+        <v>1952</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>152</v>
@@ -20916,28 +21511,28 @@
         <v>153</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>1881</v>
+        <v>1925</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>1909</v>
+        <v>1953</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>1910</v>
+        <v>1954</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>1911</v>
+        <v>1955</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>1912</v>
+        <v>1956</v>
       </c>
       <c r="M15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>1913</v>
+        <v>1957</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>152</v>
@@ -20946,28 +21541,28 @@
         <v>153</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1881</v>
+        <v>1925</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>1909</v>
+        <v>1953</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>1910</v>
+        <v>1954</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>1914</v>
+        <v>1958</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>1915</v>
+        <v>1959</v>
       </c>
       <c r="M16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>1916</v>
+        <v>1960</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>194</v>
@@ -20976,25 +21571,25 @@
         <v>195</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>1881</v>
+        <v>1925</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>1904</v>
+        <v>1948</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>1905</v>
+        <v>1949</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>1906</v>
+        <v>1950</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>1907</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>1384</v>
+        <v>1951</v>
+      </c>
+      <c r="J17" s="25" t="s">
+        <v>1961</v>
       </c>
       <c r="M17" s="11" t="s">
         <v>198</v>
@@ -21002,7 +21597,7 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>1917</v>
+        <v>1962</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>792</v>
@@ -21011,28 +21606,28 @@
         <v>793</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1887</v>
+        <v>1931</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>1904</v>
+        <v>1948</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>1905</v>
+        <v>1949</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>1906</v>
+        <v>1950</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>1907</v>
+        <v>1951</v>
       </c>
       <c r="J18" s="8"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>1918</v>
+        <v>1963</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>792</v>
@@ -21041,30 +21636,30 @@
         <v>793</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>1887</v>
+        <v>1931</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>1919</v>
+        <v>1964</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>1920</v>
+        <v>1965</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>1895</v>
+        <v>1939</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>1896</v>
+        <v>1940</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>1921</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>1922</v>
+        <v>1967</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>252</v>
@@ -21073,24 +21668,24 @@
         <v>253</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>1909</v>
+        <v>1953</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>1910</v>
+        <v>1954</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>1923</v>
+        <v>1968</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>1924</v>
+        <v>1969</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>1925</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>1926</v>
+        <v>1971</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>750</v>
@@ -21099,25 +21694,25 @@
         <v>751</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>1665</v>
+        <v>1697</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>1927</v>
+        <v>1972</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>1928</v>
+        <v>1973</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>1929</v>
+        <v>1974</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>1930</v>
+        <v>1975</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>1796</v>
+        <v>1825</v>
       </c>
       <c r="M21" s="11" t="s">
         <v>752</v>
@@ -21125,7 +21720,7 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
-        <v>1931</v>
+        <v>1976</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>479</v>
@@ -21134,24 +21729,24 @@
         <v>480</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>1927</v>
+        <v>1972</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>1928</v>
+        <v>1973</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>1929</v>
+        <v>1974</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>1930</v>
+        <v>1975</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>1796</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
-        <v>1932</v>
+        <v>1977</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>599</v>
@@ -21160,19 +21755,19 @@
         <v>600</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>1919</v>
+        <v>1964</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>1920</v>
+        <v>1965</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>1895</v>
+        <v>1939</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>1896</v>
+        <v>1940</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>1933</v>
+        <v>1978</v>
       </c>
     </row>
   </sheetData>
@@ -21202,7 +21797,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1934</v>
+        <v>1979</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -21214,30 +21809,30 @@
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1935</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>1936</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>1656</v>
+        <v>1980</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>1981</v>
+      </c>
+      <c r="H1" s="27" t="s">
+        <v>1688</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>1660</v>
+        <v>1692</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>1661</v>
+        <v>1693</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>1662</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>1937</v>
+        <v>1982</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>177</v>
@@ -21246,30 +21841,30 @@
         <v>178</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1938</v>
+        <v>1983</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1939</v>
+        <v>1984</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1940</v>
+        <v>1985</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1733</v>
+        <v>1762</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>1941</v>
+        <v>1986</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>1942</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>1943</v>
+        <v>1988</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>267</v>
@@ -21278,27 +21873,27 @@
         <v>268</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>1938</v>
+        <v>1983</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1944</v>
+        <v>1989</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1945</v>
+        <v>1990</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1733</v>
+        <v>1762</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>1946</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>1947</v>
+        <v>1992</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>267</v>
@@ -21307,24 +21902,24 @@
         <v>268</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1938</v>
+        <v>1983</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1948</v>
+        <v>1993</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1949</v>
+        <v>1994</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1763</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>1950</v>
+        <v>1995</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>267</v>
@@ -21333,27 +21928,27 @@
         <v>268</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>1938</v>
+        <v>1983</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1951</v>
+        <v>1996</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1952</v>
+        <v>1997</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1770</v>
+        <v>1799</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>1953</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>1954</v>
+        <v>1999</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>220</v>
@@ -21362,30 +21957,30 @@
         <v>221</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>1955</v>
+        <v>2000</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>1939</v>
+        <v>1984</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1940</v>
+        <v>1985</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1738</v>
+        <v>1767</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>1941</v>
+        <v>1986</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>1942</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>1956</v>
+        <v>2001</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>277</v>
@@ -21394,27 +21989,27 @@
         <v>278</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>1938</v>
+        <v>1983</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>1957</v>
+        <v>2002</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>1958</v>
+        <v>2003</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1809</v>
-      </c>
-      <c r="K7" s="26" t="s">
-        <v>1959</v>
+        <v>1838</v>
+      </c>
+      <c r="K7" s="28" t="s">
+        <v>2004</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>1960</v>
+        <v>2005</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>194</v>
@@ -21423,30 +22018,30 @@
         <v>195</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>1938</v>
+        <v>1983</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>1961</v>
+        <v>2006</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1962</v>
+        <v>2007</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1821</v>
+        <v>1850</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>1963</v>
+        <v>2008</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>1964</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>1965</v>
+        <v>2010</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>226</v>
@@ -21455,25 +22050,57 @@
         <v>227</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>1955</v>
+        <v>2000</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>1961</v>
+        <v>2006</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1962</v>
+        <v>2007</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1966</v>
+        <v>2011</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>1963</v>
+        <v>2008</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>1964</v>
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>1983</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>2013</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>2014</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>1867</v>
+      </c>
+      <c r="J10" s="6">
+        <v>1757.0</v>
+      </c>
+      <c r="K10" s="6">
+        <v>1758.0</v>
       </c>
     </row>
     <row r="13">
@@ -21502,7 +22129,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1967</v>
+        <v>2015</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -21511,36 +22138,36 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1935</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>1656</v>
+        <v>1980</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>1688</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1934</v>
+        <v>1979</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>1660</v>
+        <v>1692</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>1661</v>
+        <v>1693</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>1662</v>
+        <v>1694</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>1663</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>1968</v>
+        <v>2016</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>493</v>
@@ -21549,27 +22176,27 @@
         <v>494</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1939</v>
+        <v>1984</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1733</v>
+        <v>1762</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>1969</v>
+        <v>2017</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1937</v>
+        <v>1982</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>1941</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>1970</v>
+        <v>2018</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>581</v>
@@ -21578,27 +22205,27 @@
         <v>582</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1939</v>
+        <v>1984</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1733</v>
+        <v>1762</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>1971</v>
+        <v>2019</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1954</v>
+        <v>1999</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>1941</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>1972</v>
+        <v>2020</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>896</v>
@@ -21607,27 +22234,27 @@
         <v>897</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>1957</v>
+        <v>2002</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1809</v>
+        <v>1838</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1973</v>
+        <v>2021</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1956</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>1959</v>
+        <v>2001</v>
+      </c>
+      <c r="L4" s="28" t="s">
+        <v>2004</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>1974</v>
+        <v>2022</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>265</v>
@@ -21636,26 +22263,26 @@
         <v>266</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1961</v>
+        <v>2006</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1821</v>
+        <v>1850</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>1969</v>
+        <v>2017</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1960</v>
+        <v>2005</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>1963</v>
+        <v>2008</v>
       </c>
       <c r="K5" s="11"/>
       <c r="L5" s="11" t="s">
-        <v>1964</v>
+        <v>2009</v>
       </c>
     </row>
   </sheetData>

--- a/PERSONAL_CLAUDE.xlsx
+++ b/PERSONAL_CLAUDE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4401" uniqueCount="2023">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4403" uniqueCount="2025">
   <si>
     <t>id_persona</t>
   </si>
@@ -5904,10 +5904,16 @@
     <t>DEST016</t>
   </si>
   <si>
-    <t>31/06/1776</t>
+    <t>31/01/1776</t>
+  </si>
+  <si>
+    <t>02/03/1783</t>
   </si>
   <si>
     <t>DEST017</t>
+  </si>
+  <si>
+    <t>13/11/1795</t>
   </si>
   <si>
     <t>DEST018</t>
@@ -6170,7 +6176,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -6241,9 +6247,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -21588,16 +21591,16 @@
       <c r="I17" s="7" t="s">
         <v>1951</v>
       </c>
-      <c r="J17" s="25" t="s">
+      <c r="J17" s="11" t="s">
         <v>1961</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>198</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>792</v>
@@ -21623,11 +21626,16 @@
       <c r="I18" s="7" t="s">
         <v>1951</v>
       </c>
-      <c r="J18" s="8"/>
+      <c r="J18" s="11" t="s">
+        <v>1962</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>1964</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>792</v>
@@ -21642,10 +21650,10 @@
         <v>1931</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>1939</v>
@@ -21654,12 +21662,12 @@
         <v>1940</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>252</v>
@@ -21674,18 +21682,18 @@
         <v>1954</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>750</v>
@@ -21700,16 +21708,16 @@
         <v>1697</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>1825</v>
@@ -21720,7 +21728,7 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>479</v>
@@ -21729,16 +21737,16 @@
         <v>480</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="M22" s="11" t="s">
         <v>1825</v>
@@ -21746,7 +21754,7 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>599</v>
@@ -21755,10 +21763,10 @@
         <v>600</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>1939</v>
@@ -21767,7 +21775,7 @@
         <v>1940</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
     </row>
   </sheetData>
@@ -21797,7 +21805,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -21812,12 +21820,12 @@
         <v>1463</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1980</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>1981</v>
-      </c>
-      <c r="H1" s="27" t="s">
+        <v>1982</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>1983</v>
+      </c>
+      <c r="H1" s="26" t="s">
         <v>1688</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -21832,7 +21840,7 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>177</v>
@@ -21841,30 +21849,30 @@
         <v>178</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>1479</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>1762</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>267</v>
@@ -21873,27 +21881,27 @@
         <v>268</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>1493</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>1762</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>267</v>
@@ -21902,16 +21910,16 @@
         <v>268</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>1471</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>1792</v>
@@ -21919,7 +21927,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>267</v>
@@ -21928,27 +21936,27 @@
         <v>268</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>1493</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>1799</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>220</v>
@@ -21957,30 +21965,30 @@
         <v>221</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>1467</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>1767</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>277</v>
@@ -21989,27 +21997,27 @@
         <v>278</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>1467</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>1838</v>
       </c>
-      <c r="K7" s="28" t="s">
-        <v>2004</v>
+      <c r="K7" s="27" t="s">
+        <v>2006</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>194</v>
@@ -22018,30 +22026,30 @@
         <v>195</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>1479</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>1850</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>226</v>
@@ -22050,30 +22058,30 @@
         <v>227</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>1467</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="H9" s="6" t="s">
+        <v>2013</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>2010</v>
+      </c>
+      <c r="K9" s="11" t="s">
         <v>2011</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>2008</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>2009</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>1292</v>
@@ -22082,16 +22090,16 @@
         <v>1293</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>1471</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>1867</v>
@@ -22129,7 +22137,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -22141,16 +22149,16 @@
         <v>1463</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1980</v>
-      </c>
-      <c r="F1" s="27" t="s">
+        <v>1982</v>
+      </c>
+      <c r="F1" s="26" t="s">
         <v>1688</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>1692</v>
@@ -22167,7 +22175,7 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>493</v>
@@ -22179,24 +22187,24 @@
         <v>1475</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>1762</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>581</v>
@@ -22208,24 +22216,24 @@
         <v>1475</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>1762</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>896</v>
@@ -22237,24 +22245,24 @@
         <v>1530</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>1838</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>2001</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>2004</v>
+        <v>2003</v>
+      </c>
+      <c r="L4" s="27" t="s">
+        <v>2006</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>265</v>
@@ -22266,23 +22274,23 @@
         <v>1471</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>1850</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="K5" s="11"/>
       <c r="L5" s="11" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
     </row>
   </sheetData>
